--- a/Design Files/OLED-v2.0/BOM/eSpark_BOM_OLED-v2.0.xlsx
+++ b/Design Files/OLED-v2.0/BOM/eSpark_BOM_OLED-v2.0.xlsx
@@ -13,13 +13,18 @@
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="20 Boards" sheetId="2" r:id="rId2"/>
+    <sheet name="50 Boards" sheetId="6" r:id="rId3"/>
+    <sheet name="100 Boards" sheetId="3" r:id="rId4"/>
+    <sheet name="500 Boards" sheetId="4" r:id="rId5"/>
+    <sheet name="1000 Boards" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="152">
   <si>
     <t>Component list</t>
   </si>
@@ -415,6 +420,66 @@
   </si>
   <si>
     <t>C2857498</t>
+  </si>
+  <si>
+    <t>Quantity (20 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (20 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (20 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (20 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (50 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (50 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (50 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (50 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (100 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (100 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (100 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (100 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (500 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (500 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (500 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (500 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (1000 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (1000 Boards)</t>
   </si>
 </sst>
 </file>
@@ -886,7 +951,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1097,6 +1162,35 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1163,6 +1257,276 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29927550" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20307300" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18116550" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20307300" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20307300" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20307300" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2736,4 +3100,6504 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
   <drawing r:id="rId17"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="68"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="69"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="69"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="69"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="69"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="69"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="37">
+        <v>4</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*20</f>
+        <v>80</v>
+      </c>
+      <c r="N10" s="37">
+        <v>100</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="38">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.24</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="77"/>
+    </row>
+    <row r="11" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B26" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="51">
+        <v>4</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M26" si="1">L11*20</f>
+        <v>80</v>
+      </c>
+      <c r="N11" s="51">
+        <v>85</v>
+      </c>
+      <c r="O11" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="52">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>6.7149999999999999</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N12" s="37">
+        <v>50</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.46E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>0.73</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N13" s="51">
+        <v>40</v>
+      </c>
+      <c r="O13" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P13" s="52">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>1.1559999999999999</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N14" s="37">
+        <v>50</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P14" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>0.49500000000000005</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="S15" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="78" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="76"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N16" s="37">
+        <v>25</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="38">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>2.4375</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="51">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N17" s="51">
+        <v>25</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="52">
+        <v>0.1178</v>
+      </c>
+      <c r="Q17" s="52">
+        <f t="shared" ref="Q17" si="4">P17*N17</f>
+        <v>2.9449999999999998</v>
+      </c>
+      <c r="R17" s="51"/>
+      <c r="S17" s="59"/>
+    </row>
+    <row r="18" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="76"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N18" s="37">
+        <v>21</v>
+      </c>
+      <c r="O18" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="38">
+        <v>1.6689000000000001</v>
+      </c>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>35.046900000000001</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" s="78" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="76"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="51">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N19" s="51">
+        <v>40</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P19" s="52">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="Q19" s="52">
+        <f t="shared" ref="Q19" si="5">P19*N19</f>
+        <v>0.752</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="76"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="37">
+        <v>4</v>
+      </c>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N20" s="37">
+        <v>100</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P20" s="38">
+        <v>2.12E-2</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>2.12</v>
+      </c>
+      <c r="R20" s="37"/>
+      <c r="S20" s="59"/>
+    </row>
+    <row r="21" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="76"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N21" s="51">
+        <v>100</v>
+      </c>
+      <c r="O21" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P21" s="52">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="6">P21*N21</f>
+        <v>0.05</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="76"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N22" s="37">
+        <v>100</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="76"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N23" s="51">
+        <v>100</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" s="52">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="7">P23*N23</f>
+        <v>0.06</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="76"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="64">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="P24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="62"/>
+    </row>
+    <row r="25" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="76"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="51">
+        <v>3</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="N25" s="51">
+        <v>70</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P25" s="52">
+        <v>5.5500000000000001E-2</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25:Q26" si="8">P25*N25</f>
+        <v>3.8850000000000002</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="39"/>
+    </row>
+    <row r="26" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="76"/>
+      <c r="B26" s="47">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="51">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N26" s="51">
+        <v>25</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P26" s="52">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="Q26" s="52">
+        <f t="shared" si="8"/>
+        <v>2.08</v>
+      </c>
+      <c r="R26" s="51"/>
+      <c r="S26" s="39"/>
+    </row>
+    <row r="27" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="48">
+        <f>SUM(Q10:Q26)</f>
+        <v>58.782399999999996</v>
+      </c>
+      <c r="R27" s="70"/>
+      <c r="S27" s="71"/>
+    </row>
+    <row r="28" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="49">
+        <f>Q27/20</f>
+        <v>2.93912</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S28"/>
+    <mergeCell ref="N28:P28"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O16" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="68"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="69"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="69"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="69"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="69"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="69"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="37">
+        <v>4</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*50</f>
+        <v>200</v>
+      </c>
+      <c r="N10" s="37">
+        <v>200</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="38">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.48</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="77"/>
+    </row>
+    <row r="11" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B26" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="51">
+        <v>4</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M26" si="1">L11*50</f>
+        <v>200</v>
+      </c>
+      <c r="N11" s="51">
+        <v>205</v>
+      </c>
+      <c r="O11" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="52">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>14.472999999999999</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N12" s="37">
+        <v>100</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>1.48</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N13" s="51">
+        <v>60</v>
+      </c>
+      <c r="O13" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P13" s="52">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>1.734</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N14" s="37">
+        <v>100</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P14" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" s="78" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="S15" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="78" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="76"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N16" s="37">
+        <v>55</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="38">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>4.3560000000000008</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="51">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N17" s="51">
+        <v>55</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="52">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="Q17" s="52">
+        <f t="shared" ref="Q17" si="4">P17*N17</f>
+        <v>5.4284999999999997</v>
+      </c>
+      <c r="R17" s="51"/>
+      <c r="S17" s="59"/>
+    </row>
+    <row r="18" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="76"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N18" s="37">
+        <v>51</v>
+      </c>
+      <c r="O18" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="38">
+        <v>1.6689000000000001</v>
+      </c>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>85.113900000000001</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" s="78" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="76"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="51">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N19" s="51">
+        <v>60</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P19" s="52">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="Q19" s="52">
+        <f t="shared" ref="Q19" si="5">P19*N19</f>
+        <v>1.1280000000000001</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="79"/>
+      <c r="B20" s="80">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="81" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="81" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="81" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="81">
+        <v>4</v>
+      </c>
+      <c r="M20" s="81">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="N20" s="81">
+        <v>300</v>
+      </c>
+      <c r="O20" s="82" t="s">
+        <v>117</v>
+      </c>
+      <c r="P20" s="83">
+        <v>2.12E-2</v>
+      </c>
+      <c r="Q20" s="83">
+        <f>P20*N20</f>
+        <v>6.36</v>
+      </c>
+      <c r="R20" s="81"/>
+      <c r="S20" s="85"/>
+    </row>
+    <row r="21" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="76"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N21" s="51">
+        <v>100</v>
+      </c>
+      <c r="O21" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P21" s="52">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="6">P21*N21</f>
+        <v>0.05</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="76"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N22" s="37">
+        <v>100</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="76"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N23" s="51">
+        <v>100</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" s="52">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="7">P23*N23</f>
+        <v>0.06</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="76"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="64">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="P24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="62"/>
+    </row>
+    <row r="25" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="76"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="51">
+        <v>3</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="N25" s="51">
+        <v>160</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P25" s="52">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25:Q26" si="8">P25*N25</f>
+        <v>7.2640000000000002</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="39"/>
+    </row>
+    <row r="26" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="76"/>
+      <c r="B26" s="47">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="51">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N26" s="51">
+        <v>55</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P26" s="52">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="Q26" s="52">
+        <f t="shared" si="8"/>
+        <v>3.399</v>
+      </c>
+      <c r="R26" s="51"/>
+      <c r="S26" s="39"/>
+    </row>
+    <row r="27" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="48">
+        <f>SUM(Q10:Q26)</f>
+        <v>132.29640000000001</v>
+      </c>
+      <c r="R27" s="70"/>
+      <c r="S27" s="71"/>
+    </row>
+    <row r="28" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="49">
+        <f>Q27/50</f>
+        <v>2.6459280000000001</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S28"/>
+    <mergeCell ref="N28:P28"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O16" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="68"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="69"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="69"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="69"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="69"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="69"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="37">
+        <v>4</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*100</f>
+        <v>400</v>
+      </c>
+      <c r="N10" s="37">
+        <v>500</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="38">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>1.2</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="77"/>
+    </row>
+    <row r="11" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B26" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="51">
+        <v>4</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M26" si="1">L11*100</f>
+        <v>400</v>
+      </c>
+      <c r="N11" s="51">
+        <v>405</v>
+      </c>
+      <c r="O11" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="52">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>28.593</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N12" s="37">
+        <v>150</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.46E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>2.19</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N13" s="51">
+        <v>120</v>
+      </c>
+      <c r="O13" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P13" s="52">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>3.468</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N14" s="37">
+        <v>150</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P14" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" s="78" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="S15" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="78" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="76"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N16" s="37">
+        <v>105</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="38">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>8.3160000000000007</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="51">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N17" s="51">
+        <v>105</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="52">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="Q17" s="52">
+        <f t="shared" ref="Q17" si="4">P17*N17</f>
+        <v>10.3635</v>
+      </c>
+      <c r="R17" s="51"/>
+      <c r="S17" s="59"/>
+    </row>
+    <row r="18" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="76"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N18" s="37">
+        <v>101</v>
+      </c>
+      <c r="O18" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="38">
+        <v>1.6371</v>
+      </c>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>165.34710000000001</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" s="78" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="76"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="51">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N19" s="51">
+        <v>120</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P19" s="52">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="Q19" s="52">
+        <f t="shared" ref="Q19" si="5">P19*N19</f>
+        <v>2.2560000000000002</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="76"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="37">
+        <v>4</v>
+      </c>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="N20" s="37">
+        <v>500</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P20" s="38">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="R20" s="37"/>
+      <c r="S20" s="59"/>
+    </row>
+    <row r="21" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="76"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N21" s="51">
+        <v>200</v>
+      </c>
+      <c r="O21" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P21" s="52">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="6">P21*N21</f>
+        <v>0.1</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="76"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N22" s="37">
+        <v>200</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="76"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N23" s="51">
+        <v>200</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" s="52">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="7">P23*N23</f>
+        <v>0.08</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" s="78" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="76"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="P24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="62"/>
+    </row>
+    <row r="25" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="76"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="51">
+        <v>3</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="N25" s="51">
+        <v>320</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P25" s="52">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25:Q26" si="8">P25*N25</f>
+        <v>12.896000000000001</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="39"/>
+    </row>
+    <row r="26" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="76"/>
+      <c r="B26" s="47">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="51">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N26" s="51">
+        <v>105</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P26" s="52">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="Q26" s="52">
+        <f t="shared" si="8"/>
+        <v>6.4889999999999999</v>
+      </c>
+      <c r="R26" s="51"/>
+      <c r="S26" s="39"/>
+    </row>
+    <row r="27" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="48">
+        <f>SUM(Q10:Q26)</f>
+        <v>251.37359999999998</v>
+      </c>
+      <c r="R27" s="70"/>
+      <c r="S27" s="71"/>
+    </row>
+    <row r="28" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="49">
+        <f>Q27/100</f>
+        <v>2.5137359999999997</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S28"/>
+    <mergeCell ref="N28:P28"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O16" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="68"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="69"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="69"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="69"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="69"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="69"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="37">
+        <v>4</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*500</f>
+        <v>2000</v>
+      </c>
+      <c r="N10" s="37">
+        <v>2100</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.9E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>3.99</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="77"/>
+    </row>
+    <row r="11" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B26" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="51">
+        <v>4</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M26" si="1">L11*500</f>
+        <v>2000</v>
+      </c>
+      <c r="N11" s="51">
+        <v>2005</v>
+      </c>
+      <c r="O11" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="52">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>128.92149999999998</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N12" s="37">
+        <v>550</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.21E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>6.6549999999999994</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N13" s="51">
+        <v>520</v>
+      </c>
+      <c r="O13" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P13" s="52">
+        <v>2.35E-2</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>12.22</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N14" s="37">
+        <v>550</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P14" s="38">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>3.96</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" s="78" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="S15" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="78" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="76"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N16" s="37">
+        <v>505</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="38">
+        <v>6.3200000000000006E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>31.916000000000004</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="51">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N17" s="51">
+        <v>505</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="52">
+        <v>7.4200000000000002E-2</v>
+      </c>
+      <c r="Q17" s="52">
+        <f t="shared" ref="Q17" si="4">P17*N17</f>
+        <v>37.471000000000004</v>
+      </c>
+      <c r="R17" s="51"/>
+      <c r="S17" s="59"/>
+    </row>
+    <row r="18" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="76"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N18" s="37">
+        <v>501</v>
+      </c>
+      <c r="O18" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="38">
+        <v>1.3315999999999999</v>
+      </c>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>667.13159999999993</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" s="78" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="76"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="51">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N19" s="51">
+        <v>520</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P19" s="52">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Q19" s="52">
+        <f t="shared" ref="Q19" si="5">P19*N19</f>
+        <v>7.8</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="76"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="37">
+        <v>4</v>
+      </c>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="N20" s="37">
+        <v>2020</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P20" s="38">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>30.299999999999997</v>
+      </c>
+      <c r="R20" s="37"/>
+      <c r="S20" s="59"/>
+    </row>
+    <row r="21" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="76"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N21" s="51">
+        <v>600</v>
+      </c>
+      <c r="O21" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P21" s="52">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="6">P21*N21</f>
+        <v>0.3</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="76"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N22" s="37">
+        <v>600</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.42</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="76"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N23" s="51">
+        <v>600</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" s="52">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="7">P23*N23</f>
+        <v>0.36</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="76"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="64">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="P24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="62"/>
+    </row>
+    <row r="25" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="76"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="51">
+        <v>3</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="N25" s="51">
+        <v>1520</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P25" s="52">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25:Q26" si="8">P25*N25</f>
+        <v>61.256</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="39"/>
+    </row>
+    <row r="26" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="76"/>
+      <c r="B26" s="47">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="51">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N26" s="51">
+        <v>505</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P26" s="52">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q26" s="52">
+        <f t="shared" si="8"/>
+        <v>24.391500000000001</v>
+      </c>
+      <c r="R26" s="51"/>
+      <c r="S26" s="39"/>
+    </row>
+    <row r="27" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="48">
+        <f>SUM(Q10:Q26)</f>
+        <v>1017.0925999999997</v>
+      </c>
+      <c r="R27" s="70"/>
+      <c r="S27" s="71"/>
+    </row>
+    <row r="28" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="49">
+        <f>Q27/500</f>
+        <v>2.0341851999999996</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S28"/>
+    <mergeCell ref="N28:P28"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O16" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="68"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="69"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="69"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="69"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="69"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="69"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="37">
+        <v>4</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*1000</f>
+        <v>4000</v>
+      </c>
+      <c r="N10" s="37">
+        <v>4100</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>6.5600000000000005</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="77"/>
+    </row>
+    <row r="11" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B26" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="51">
+        <v>4</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M26" si="1">L11*1000</f>
+        <v>4000</v>
+      </c>
+      <c r="N11" s="51">
+        <v>4005</v>
+      </c>
+      <c r="O11" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="52">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>227.48400000000001</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N12" s="37">
+        <v>1050</v>
+      </c>
+      <c r="O12" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.21E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>12.705</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N13" s="51">
+        <v>1020</v>
+      </c>
+      <c r="O13" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P13" s="52">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>20.808</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N14" s="37">
+        <v>1050</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P14" s="38">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>7.56</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="S15" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="78" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="76"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N16" s="37">
+        <v>1005</v>
+      </c>
+      <c r="O16" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="38">
+        <v>6.3200000000000006E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>63.516000000000005</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="51">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N17" s="51">
+        <v>1005</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="52">
+        <v>7.4200000000000002E-2</v>
+      </c>
+      <c r="Q17" s="52">
+        <f t="shared" ref="Q17" si="4">P17*N17</f>
+        <v>74.570999999999998</v>
+      </c>
+      <c r="R17" s="51"/>
+      <c r="S17" s="59"/>
+    </row>
+    <row r="18" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="76"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N18" s="37">
+        <v>1001</v>
+      </c>
+      <c r="O18" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="38">
+        <v>1.3315999999999999</v>
+      </c>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>1332.9315999999999</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" s="78" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="76"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="51">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N19" s="51">
+        <v>1020</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P19" s="52">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="Q19" s="52">
+        <f t="shared" ref="Q19" si="5">P19*N19</f>
+        <v>13.056000000000001</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="76"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="37">
+        <v>4</v>
+      </c>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="N20" s="37">
+        <v>4020</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P20" s="38">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>60.3</v>
+      </c>
+      <c r="R20" s="37"/>
+      <c r="S20" s="59"/>
+    </row>
+    <row r="21" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="76"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N21" s="51">
+        <v>1100</v>
+      </c>
+      <c r="O21" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P21" s="52">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="6">P21*N21</f>
+        <v>0.44</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="76"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N22" s="37">
+        <v>1100</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" s="38">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" s="78" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="76"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N23" s="51">
+        <v>1100</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" s="52">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="7">P23*N23</f>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="76"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="64">
+        <v>1</v>
+      </c>
+      <c r="M24" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="P24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="62"/>
+    </row>
+    <row r="25" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="76"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="51">
+        <v>3</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="N25" s="51">
+        <v>3010</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P25" s="52">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25:Q26" si="8">P25*N25</f>
+        <v>107.758</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="39"/>
+    </row>
+    <row r="26" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="76"/>
+      <c r="B26" s="47">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="51">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N26" s="51">
+        <v>1005</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P26" s="52">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q26" s="52">
+        <f t="shared" si="8"/>
+        <v>48.541499999999999</v>
+      </c>
+      <c r="R26" s="51"/>
+      <c r="S26" s="39"/>
+    </row>
+    <row r="27" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="48">
+        <f>SUM(Q10:Q26)</f>
+        <v>1977.2211000000002</v>
+      </c>
+      <c r="R27" s="70"/>
+      <c r="S27" s="71"/>
+    </row>
+    <row r="28" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="49">
+        <f>Q27/1000</f>
+        <v>1.9772211000000002</v>
+      </c>
+      <c r="R28" s="72"/>
+      <c r="S28" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S28"/>
+    <mergeCell ref="N28:P28"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O16" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId16"/>
+</worksheet>
 </file>